--- a/314e-ig/output/StructureDefinition-duration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-duration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T16:45:26+05:30</t>
+    <t>2026-05-17T00:25:02+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -333,13 +333,13 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Duration.extension:valueString</t>
-  </si>
-  <si>
-    <t>valueString</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/quantity-valueString}
+    <t>Duration.extension:quantityString</t>
+  </si>
+  <si>
+    <t>quantityString</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/quantity-quantityString}
 </t>
   </si>
   <si>
@@ -367,11 +367,13 @@
 Whenever precision is needed, precision metadata SHALL 
 be explicitly represented using the quantityPrecision extension on the 314e decimal profile. 
 The quantityPrecision extension represents the number of significant decimal places intended
-for the quantity value, irrespective of how many decimal places
+for the duration value, irrespective of how many decimal places
 are explicitly present in the decimal representation itself.
 The presence of this extension does not alter the underlying
 numeric value or computation semantics.
-The original textual representation of value may additionally
+The original textual representation of the full duration quantity may 
+be preserved using the valueString extension.
+The original textual representation of just the duration value may additionally
 be preserved using the valueString extension.</t>
   </si>
   <si>
@@ -444,20 +446,20 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>Duration.value.extension:quantityString</t>
-  </si>
-  <si>
-    <t>quantityString</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/quantity-quantityString}
+    <t>Duration.value.extension:valueString</t>
+  </si>
+  <si>
+    <t>valueString</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/quantity-valueString}
 </t>
   </si>
   <si>
-    <t>Original textual representation of the quantity value</t>
-  </si>
-  <si>
-    <t>Original textual representation of the duration quantity value
+    <t>Original textual representation of the duration value</t>
+  </si>
+  <si>
+    <t>Original textual representation of the duration value
 as received from the source system.</t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-duration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-duration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-17T00:25:02+05:30</t>
+    <t>2026-05-19T06:46:39+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-duration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-duration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T06:46:39+05:30</t>
+    <t>2026-05-19T11:54:54+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-duration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-duration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T11:54:54+05:30</t>
+    <t>2026-05-25T12:07:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-duration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-duration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:07:44+05:30</t>
+    <t>2026-05-25T12:34:12+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-duration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-duration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:34:12+05:30</t>
+    <t>2026-05-25T13:52:53+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-duration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-duration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T13:52:53+05:30</t>
+    <t>2026-05-25T14:14:21+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-duration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-duration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:14:21+05:30</t>
+    <t>2026-05-25T14:26:28+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-duration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-duration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:26:28+05:30</t>
+    <t>2026-05-25T14:41:34+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-duration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-duration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:41:34+05:30</t>
+    <t>2026-05-25T15:12:42+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-duration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-duration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:12:42+05:30</t>
+    <t>2026-05-25T15:24:41+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-duration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-duration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:24:41+05:30</t>
+    <t>2026-05-25T15:48:57+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-duration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-duration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:48:57+05:30</t>
+    <t>2026-05-25T16:36:06+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-duration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-duration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T16:36:06+05:30</t>
+    <t>2026-05-26T08:48:22+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-duration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-duration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T08:48:22+05:30</t>
+    <t>2026-05-26T12:06:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-duration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-duration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T12:06:33+05:30</t>
+    <t>2026-05-26T19:54:55+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-duration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-duration-314e.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="179">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T19:54:55+05:30</t>
+    <t>2026-06-10T16:33:40+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -262,6 +262,15 @@
   </si>
   <si>
     <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Appropriate units for Duration.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/duration-units|4.0.1</t>
   </si>
   <si>
     <t>drt-1:There SHALL be a code if there is a value and it SHALL be an expression of time.  If system is present, it SHALL be UCUM. {code.exists() implies ((system = %ucum) and value.exists())}
@@ -1104,13 +1113,13 @@
         <v>20</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="AA2" t="s" s="2">
         <v>20</v>
@@ -1140,21 +1149,21 @@
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1165,7 +1174,7 @@
         <v>75</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -1177,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1234,13 +1243,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -1249,7 +1258,7 @@
         <v>20</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AL3" t="s" s="2">
         <v>20</v>
@@ -1257,14 +1266,14 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
@@ -1283,16 +1292,16 @@
         <v>20</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="N4" t="s" s="2">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
@@ -1330,19 +1339,19 @@
         <v>20</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>75</v>
@@ -1354,10 +1363,10 @@
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AL4" t="s" s="2">
         <v>20</v>
@@ -1365,13 +1374,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>20</v>
@@ -1381,7 +1390,7 @@
         <v>75</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
@@ -1393,13 +1402,13 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1450,7 +1459,7 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>75</v>
@@ -1462,7 +1471,7 @@
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -1473,10 +1482,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1487,7 +1496,7 @@
         <v>75</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -1496,22 +1505,22 @@
         <v>20</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="O6" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="P6" t="s" s="2">
         <v>20</v>
@@ -1560,33 +1569,33 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1597,7 +1606,7 @@
         <v>75</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -1609,13 +1618,13 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1666,13 +1675,13 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
@@ -1689,10 +1698,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1715,13 +1724,13 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1760,17 +1769,17 @@
         <v>20</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AC8" s="2"/>
       <c r="AD8" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>75</v>
@@ -1782,7 +1791,7 @@
         <v>20</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>20</v>
@@ -1793,13 +1802,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="B9" t="s" s="2">
-        <v>121</v>
-      </c>
       <c r="C9" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D9" t="s" s="2">
         <v>20</v>
@@ -1809,7 +1818,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -1821,16 +1830,16 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -1880,7 +1889,7 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
@@ -1889,27 +1898,27 @@
         <v>76</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
@@ -1919,7 +1928,7 @@
         <v>75</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
@@ -1931,13 +1940,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1988,7 +1997,7 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>75</v>
@@ -2000,7 +2009,7 @@
         <v>20</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -2011,10 +2020,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2025,7 +2034,7 @@
         <v>75</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
@@ -2037,13 +2046,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2094,13 +2103,13 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
@@ -2117,10 +2126,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2131,35 +2140,35 @@
         <v>75</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q12" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="R12" t="s" s="2">
         <v>20</v>
@@ -2180,13 +2189,13 @@
         <v>20</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>20</v>
@@ -2204,33 +2213,33 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2241,7 +2250,7 @@
         <v>75</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -2250,20 +2259,20 @@
         <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -2312,33 +2321,33 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2349,7 +2358,7 @@
         <v>75</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -2358,20 +2367,20 @@
         <v>20</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -2420,33 +2429,33 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2457,7 +2466,7 @@
         <v>75</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -2466,22 +2475,22 @@
         <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
@@ -2530,25 +2539,25 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/314e-ig/output/StructureDefinition-duration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-duration-314e.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="147">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -264,15 +264,6 @@
     <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Appropriate units for Duration.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/duration-units|4.0.1</t>
-  </si>
-  <si>
     <t>drt-1:There SHALL be a code if there is a value and it SHALL be an expression of time.  If system is present, it SHALL be UCUM. {code.exists() implies ((system = %ucum) and value.exists())}
 ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
   </si>
@@ -342,48 +333,20 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Duration.extension:quantityString</t>
-  </si>
-  <si>
-    <t>quantityString</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/quantity-quantityString}
+    <t>Duration.value</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decimal
 </t>
   </si>
   <si>
-    <t>Original textual representation of the duration</t>
-  </si>
-  <si>
-    <t>Original textual representation of the duration
-as received from the source system.</t>
-  </si>
-  <si>
-    <t>Duration.value</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decimal {http://314e.com/fhir/ig/StructureDefinition/decimal-314e}
-</t>
-  </si>
-  <si>
-    <t>Numerical value with explicit precision support</t>
-  </si>
-  <si>
-    <t>The value of the measured amount.
-Whenever precision is needed, precision metadata SHALL 
-be explicitly represented using the quantityPrecision extension on the 314e decimal profile. 
-The quantityPrecision extension represents the number of significant decimal places intended
-for the duration value, irrespective of how many decimal places
-are explicitly present in the decimal representation itself.
-The presence of this extension does not alter the underlying
-numeric value or computation semantics.
-The original textual representation of the full duration quantity may 
-be preserved using the valueString extension.
-The original textual representation of just the duration value may additionally
-be preserved using the valueString extension.</t>
+    <t>Numerical value (with implicit precision)</t>
+  </si>
+  <si>
+    <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
   </si>
   <si>
     <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
@@ -403,89 +366,6 @@
   </si>
   <si>
     <t>SN.2  / CQ - N/A</t>
-  </si>
-  <si>
-    <t>Duration.value.id</t>
-  </si>
-  <si>
-    <t>xml:id (or equivalent in JSON)</t>
-  </si>
-  <si>
-    <t>unique id for the element within a resource (for internal references)</t>
-  </si>
-  <si>
-    <t>Duration.value.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>Duration.value.extension:quantityPrecision</t>
-  </si>
-  <si>
-    <t>quantityPrecision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {quantity-precision}
-</t>
-  </si>
-  <si>
-    <t>Explicit precision of the decimal value</t>
-  </si>
-  <si>
-    <t>Explicit precision of the number.
-This represents the intended or known number
-of significant decimal places irrespective
-of how many are explicitly represented
-in the decimal value itself.</t>
-  </si>
-  <si>
-    <t>Applications performing calculations SHALL ensure
-that this extension is updated appropriately
-if the numeric value changes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Duration.value.extension:valueString</t>
-  </si>
-  <si>
-    <t>valueString</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/quantity-valueString}
-</t>
-  </si>
-  <si>
-    <t>Original textual representation of the duration value</t>
-  </si>
-  <si>
-    <t>Original textual representation of the duration value
-as received from the source system.</t>
-  </si>
-  <si>
-    <t>Duration.value.value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decimal
-</t>
-  </si>
-  <si>
-    <t>Primitive value for decimal</t>
-  </si>
-  <si>
-    <t>The actual value</t>
-  </si>
-  <si>
-    <t>decimal.value</t>
   </si>
   <si>
     <t>Duration.comparator</t>
@@ -892,12 +772,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL15"/>
+  <dimension ref="A1:AL9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="35.65234375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="21.125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.9296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="17.95703125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="17.95703125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="9.984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="11.10546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
@@ -905,7 +785,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="63.00390625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="8.73046875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1113,13 +993,13 @@
         <v>20</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="AA2" t="s" s="2">
         <v>20</v>
@@ -1149,21 +1029,21 @@
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1174,25 +1054,25 @@
         <v>75</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K3" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L3" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="M3" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H3" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K3" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="L3" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>91</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1243,13 +1123,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -1258,7 +1138,7 @@
         <v>20</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="AL3" t="s" s="2">
         <v>20</v>
@@ -1266,14 +1146,14 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
@@ -1292,16 +1172,16 @@
         <v>20</v>
       </c>
       <c r="K4" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="L4" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="M4" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="N4" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="L4" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N4" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
@@ -1339,19 +1219,19 @@
         <v>20</v>
       </c>
       <c r="AB4" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AC4" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AD4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE4" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AF4" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="AC4" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AD4" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE4" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AF4" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>75</v>
@@ -1363,10 +1243,10 @@
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="AL4" t="s" s="2">
         <v>20</v>
@@ -1374,14 +1254,12 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>106</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
         <v>20</v>
       </c>
@@ -1390,7 +1268,7 @@
         <v>75</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
@@ -1399,19 +1277,23 @@
         <v>20</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L5" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M5" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N5" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="O5" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="M5" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>20</v>
       </c>
@@ -1459,33 +1341,33 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>20</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1496,36 +1378,36 @@
         <v>75</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="N6" s="2"/>
       <c r="O6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P6" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q6" s="2"/>
+      <c r="Q6" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="R6" t="s" s="2">
         <v>20</v>
       </c>
@@ -1545,13 +1427,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>20</v>
+        <v>121</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -1569,33 +1451,33 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1606,7 +1488,7 @@
         <v>75</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -1615,19 +1497,21 @@
         <v>20</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
+      <c r="O7" t="s" s="2">
+        <v>128</v>
+      </c>
       <c r="P7" t="s" s="2">
         <v>20</v>
       </c>
@@ -1675,33 +1559,33 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>20</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1712,7 +1596,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -1721,19 +1605,21 @@
         <v>20</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
+      <c r="O8" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="P8" t="s" s="2">
         <v>20</v>
       </c>
@@ -1769,47 +1655,47 @@
         <v>20</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AC8" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD8" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>102</v>
+        <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>20</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>128</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>20</v>
       </c>
@@ -1818,7 +1704,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -1827,21 +1713,23 @@
         <v>20</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O9" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="O9" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P9" t="s" s="2">
         <v>20</v>
       </c>
@@ -1889,675 +1777,25 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>133</v>
+        <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>93</v>
+        <v>146</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G10" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H10" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I10" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J10" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K10" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L10" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q10" s="2"/>
-      <c r="R10" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S10" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T10" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U10" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V10" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W10" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X10" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y10" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z10" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA10" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB10" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC10" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD10" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE10" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF10" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AG10" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH10" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI10" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ10" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK10" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL10" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G11" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K11" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q11" s="2"/>
-      <c r="R11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AG11" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL11" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G12" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="K12" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="P12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q12" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="R12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK12" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G13" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J13" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="K13" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N13" s="2"/>
-      <c r="O13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="P13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q13" s="2"/>
-      <c r="R13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G14" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J14" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="K14" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N14" s="2"/>
-      <c r="O14" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="P14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q14" s="2"/>
-      <c r="R14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G15" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="K15" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="P15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q15" s="2"/>
-      <c r="R15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>163</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/314e-ig/output/StructureDefinition-duration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-duration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-duration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-duration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-duration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-duration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-duration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-duration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-duration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-duration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-duration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-duration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
